--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/99.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/99.xlsx
@@ -426,13 +426,13 @@
         <v>-1.935385424008356</v>
       </c>
       <c r="E2">
-        <v>-9.125968564399221</v>
+        <v>-1.969476178909509</v>
       </c>
       <c r="F2">
-        <v>-4.109162209041609</v>
+        <v>-3.66569157811588</v>
       </c>
       <c r="G2">
-        <v>-6.551127159783751</v>
+        <v>-2.960661752985028</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.754864756696448</v>
       </c>
       <c r="E3">
-        <v>-9.057027076106447</v>
+        <v>-3.439853575304044</v>
       </c>
       <c r="F3">
-        <v>-4.278876465792367</v>
+        <v>-3.898477728915791</v>
       </c>
       <c r="G3">
-        <v>-5.495089617120557</v>
+        <v>-2.459163761968532</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.535217117511955</v>
       </c>
       <c r="E4">
-        <v>-10.52322016251789</v>
+        <v>-3.781852989311325</v>
       </c>
       <c r="F4">
-        <v>-4.339050730666528</v>
+        <v>-3.895253722984096</v>
       </c>
       <c r="G4">
-        <v>-5.942367493294869</v>
+        <v>-2.114857094247711</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.284904482370529</v>
       </c>
       <c r="E5">
-        <v>-11.50598959166252</v>
+        <v>-4.495490679706089</v>
       </c>
       <c r="F5">
-        <v>-4.21282410582794</v>
+        <v>-3.756232963609269</v>
       </c>
       <c r="G5">
-        <v>-4.795673971584272</v>
+        <v>-1.488551536400691</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.9976585445355607</v>
       </c>
       <c r="E6">
-        <v>-11.58454503027357</v>
+        <v>-6.630992224451214</v>
       </c>
       <c r="F6">
-        <v>-4.083365191383627</v>
+        <v>-3.837559590113916</v>
       </c>
       <c r="G6">
-        <v>-4.238575368235717</v>
+        <v>-1.61210771701737</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.6763145828032765</v>
       </c>
       <c r="E7">
-        <v>-12.94358989318953</v>
+        <v>-7.450120716854659</v>
       </c>
       <c r="F7">
-        <v>-3.970062754763517</v>
+        <v>-3.399113835853568</v>
       </c>
       <c r="G7">
-        <v>-5.1033362107309</v>
+        <v>-2.699866907037861</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.3210290163338294</v>
       </c>
       <c r="E8">
-        <v>-14.62912867511051</v>
+        <v>-8.464209072236329</v>
       </c>
       <c r="F8">
-        <v>-4.107275188098032</v>
+        <v>-3.630795772905548</v>
       </c>
       <c r="G8">
-        <v>-4.951911857764636</v>
+        <v>-2.213372308405343</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.06088825910687287</v>
       </c>
       <c r="E9">
-        <v>-13.82569134514364</v>
+        <v>-9.348108328371483</v>
       </c>
       <c r="F9">
-        <v>-4.258476261763623</v>
+        <v>-3.190064552980877</v>
       </c>
       <c r="G9">
-        <v>-5.195236954901069</v>
+        <v>-2.032229188133041</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.465291011658615</v>
       </c>
       <c r="E10">
-        <v>-15.35467172367144</v>
+        <v>-9.946736364393443</v>
       </c>
       <c r="F10">
-        <v>-4.022830586689247</v>
+        <v>-3.056259194774075</v>
       </c>
       <c r="G10">
-        <v>-3.893950888143125</v>
+        <v>-1.945231361906534</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.8836842362451118</v>
       </c>
       <c r="E11">
-        <v>-15.88075813456453</v>
+        <v>-10.71342965626207</v>
       </c>
       <c r="F11">
-        <v>-3.696048758326274</v>
+        <v>-3.200509437562776</v>
       </c>
       <c r="G11">
-        <v>-5.140765238597901</v>
+        <v>-1.528701832700972</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.302017069867211</v>
       </c>
       <c r="E12">
-        <v>-17.16096679348095</v>
+        <v>-11.86162424090689</v>
       </c>
       <c r="F12">
-        <v>-4.027558079457024</v>
+        <v>-2.996582778708996</v>
       </c>
       <c r="G12">
-        <v>-3.39622029795032</v>
+        <v>-1.524609998414433</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.707320264126008</v>
       </c>
       <c r="E13">
-        <v>-17.59962648518195</v>
+        <v>-12.46509321564305</v>
       </c>
       <c r="F13">
-        <v>-3.389618260315277</v>
+        <v>-2.653305670254075</v>
       </c>
       <c r="G13">
-        <v>-3.040296925932196</v>
+        <v>-1.619768319395244</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.081623851963707</v>
       </c>
       <c r="E14">
-        <v>-18.84136575740322</v>
+        <v>-13.0365005944049</v>
       </c>
       <c r="F14">
-        <v>-3.769141412847093</v>
+        <v>-2.427723002388908</v>
       </c>
       <c r="G14">
-        <v>-2.798345705194561</v>
+        <v>-0.5279504005436064</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.407723280731001</v>
       </c>
       <c r="E15">
-        <v>-18.72379751521608</v>
+        <v>-14.38397973470527</v>
       </c>
       <c r="F15">
-        <v>-3.581367089980501</v>
+        <v>-2.27675635669831</v>
       </c>
       <c r="G15">
-        <v>-2.886482359086578</v>
+        <v>-0.5722918474966048</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.674232302793142</v>
       </c>
       <c r="E16">
-        <v>-19.42655328257042</v>
+        <v>-16.04220276141198</v>
       </c>
       <c r="F16">
-        <v>-3.264821397613921</v>
+        <v>-2.304089995888485</v>
       </c>
       <c r="G16">
-        <v>-2.639810300409943</v>
+        <v>-0.3901853584723753</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.871226052081597</v>
       </c>
       <c r="E17">
-        <v>-20.1511227092197</v>
+        <v>-16.33403574036229</v>
       </c>
       <c r="F17">
-        <v>-3.297131868160116</v>
+        <v>-1.663347809823067</v>
       </c>
       <c r="G17">
-        <v>-1.901012405138488</v>
+        <v>-0.3944625833091137</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.994798295105296</v>
       </c>
       <c r="E18">
-        <v>-21.97086734683199</v>
+        <v>-17.05396800962772</v>
       </c>
       <c r="F18">
-        <v>-3.039227960972517</v>
+        <v>-1.356653062610578</v>
       </c>
       <c r="G18">
-        <v>-2.030971180828118</v>
+        <v>0.5037976694979553</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.048098430013457</v>
       </c>
       <c r="E19">
-        <v>-22.80878447789326</v>
+        <v>-18.09531777853556</v>
       </c>
       <c r="F19">
-        <v>-2.130593413576545</v>
+        <v>-1.286846541576664</v>
       </c>
       <c r="G19">
-        <v>-1.7834913490399</v>
+        <v>-0.06452368322872935</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.038012422023272</v>
       </c>
       <c r="E20">
-        <v>-23.32001749404119</v>
+        <v>-19.26726873782462</v>
       </c>
       <c r="F20">
-        <v>-2.036186037414291</v>
+        <v>-0.8969588561010209</v>
       </c>
       <c r="G20">
-        <v>-1.094580064499724</v>
+        <v>0.007272117881444884</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.976124305153595</v>
       </c>
       <c r="E21">
-        <v>-23.83404005017784</v>
+        <v>-20.20029740846899</v>
       </c>
       <c r="F21">
-        <v>-2.079947858936786</v>
+        <v>-0.206286824831863</v>
       </c>
       <c r="G21">
-        <v>-0.6648017320459988</v>
+        <v>0.2595754145203806</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.876248632722263</v>
       </c>
       <c r="E22">
-        <v>-24.4695026937782</v>
+        <v>-21.43691950506159</v>
       </c>
       <c r="F22">
-        <v>-1.873806974015324</v>
+        <v>-0.1754467064256374</v>
       </c>
       <c r="G22">
-        <v>-1.537964739119853</v>
+        <v>0.5025131778287181</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.748379372980812</v>
       </c>
       <c r="E23">
-        <v>-24.65290589108884</v>
+        <v>-20.91407548155799</v>
       </c>
       <c r="F23">
-        <v>-1.875920139259865</v>
+        <v>-0.01341555733584575</v>
       </c>
       <c r="G23">
-        <v>-0.8782160502351158</v>
+        <v>0.08838379413912824</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.600176968616813</v>
       </c>
       <c r="E24">
-        <v>-25.05942700275741</v>
+        <v>-21.84283832968713</v>
       </c>
       <c r="F24">
-        <v>-1.130562605527495</v>
+        <v>0.5971516893477943</v>
       </c>
       <c r="G24">
-        <v>-1.264563335759142</v>
+        <v>0.3632153531728044</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.437889161277865</v>
       </c>
       <c r="E25">
-        <v>-24.65491653354825</v>
+        <v>-21.73824869400598</v>
       </c>
       <c r="F25">
-        <v>-0.8780455715603025</v>
+        <v>0.723952372796523</v>
       </c>
       <c r="G25">
-        <v>-1.802225726246636</v>
+        <v>-0.141159501917318</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.263168883649357</v>
       </c>
       <c r="E26">
-        <v>-26.20894843028648</v>
+        <v>-21.81866533543419</v>
       </c>
       <c r="F26">
-        <v>-1.006794575140416</v>
+        <v>1.134338838021843</v>
       </c>
       <c r="G26">
-        <v>-1.783031183209942</v>
+        <v>-0.2501294188879685</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.079539125595638</v>
       </c>
       <c r="E27">
-        <v>-25.36131772247876</v>
+        <v>-21.91255418703522</v>
       </c>
       <c r="F27">
-        <v>-0.7441963098811528</v>
+        <v>1.079814038834774</v>
       </c>
       <c r="G27">
-        <v>-1.51458566652152</v>
+        <v>-0.373506830045527</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.891661226284786</v>
       </c>
       <c r="E28">
-        <v>-25.99017332250192</v>
+        <v>-22.51245019577933</v>
       </c>
       <c r="F28">
-        <v>-1.080305555199649</v>
+        <v>0.8234757460384667</v>
       </c>
       <c r="G28">
-        <v>-1.987152800070325</v>
+        <v>-0.5973063295913379</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.701703865891376</v>
       </c>
       <c r="E29">
-        <v>-25.28162110841777</v>
+        <v>-22.62111998654139</v>
       </c>
       <c r="F29">
-        <v>-1.207322442540509</v>
+        <v>1.226186558909447</v>
       </c>
       <c r="G29">
-        <v>-1.70191288586118</v>
+        <v>-0.9671604772387149</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.515949006842458</v>
       </c>
       <c r="E30">
-        <v>-25.71171292729626</v>
+        <v>-21.30293554459664</v>
       </c>
       <c r="F30">
-        <v>-0.7169653882489246</v>
+        <v>0.8162921439213895</v>
       </c>
       <c r="G30">
-        <v>-2.982339205176176</v>
+        <v>-0.8185434668897528</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.339204315217461</v>
       </c>
       <c r="E31">
-        <v>-25.38583488075628</v>
+        <v>-21.88648829064707</v>
       </c>
       <c r="F31">
-        <v>-1.184744460609805</v>
+        <v>0.8598609558390322</v>
       </c>
       <c r="G31">
-        <v>-2.112605923281006</v>
+        <v>-1.625389625720926</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.175902066800065</v>
       </c>
       <c r="E32">
-        <v>-24.87183043851566</v>
+        <v>-21.51390356319198</v>
       </c>
       <c r="F32">
-        <v>-0.8771666737459323</v>
+        <v>1.12441665327111</v>
       </c>
       <c r="G32">
-        <v>-2.330641763042946</v>
+        <v>-1.154030841293956</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.036060030684517</v>
       </c>
       <c r="E33">
-        <v>-24.46498327671854</v>
+        <v>-20.76880656386593</v>
       </c>
       <c r="F33">
-        <v>-0.7629132713474076</v>
+        <v>1.128985927864953</v>
       </c>
       <c r="G33">
-        <v>-2.148588242747345</v>
+        <v>-0.8825164488906292</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.925125242586615</v>
       </c>
       <c r="E34">
-        <v>-25.17044254305545</v>
+        <v>-20.52771513617157</v>
       </c>
       <c r="F34">
-        <v>-0.7276695518278998</v>
+        <v>0.8251440779877049</v>
       </c>
       <c r="G34">
-        <v>-3.126592916504378</v>
+        <v>-1.635490100161243</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.8511882582730347</v>
       </c>
       <c r="E35">
-        <v>-23.50296331547706</v>
+        <v>-20.51713662088965</v>
       </c>
       <c r="F35">
-        <v>-0.726446053173965</v>
+        <v>0.8921440902609346</v>
       </c>
       <c r="G35">
-        <v>-3.734018433140934</v>
+        <v>-1.665639238387385</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.8227257346900341</v>
       </c>
       <c r="E36">
-        <v>-22.48873457740116</v>
+        <v>-20.16426886926396</v>
       </c>
       <c r="F36">
-        <v>-1.146211294133781</v>
+        <v>0.7317208022999767</v>
       </c>
       <c r="G36">
-        <v>-3.012041419754516</v>
+        <v>-1.887872849893121</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.8418480881892481</v>
       </c>
       <c r="E37">
-        <v>-22.2092099908037</v>
+        <v>-18.42319741058693</v>
       </c>
       <c r="F37">
-        <v>-0.9842994299499923</v>
+        <v>0.6683415839443838</v>
       </c>
       <c r="G37">
-        <v>-3.621582374990667</v>
+        <v>-1.95569599635617</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9117900325772713</v>
       </c>
       <c r="E38">
-        <v>-21.78914874185219</v>
+        <v>-18.74280804910028</v>
       </c>
       <c r="F38">
-        <v>-1.007453955593044</v>
+        <v>0.9164732408811561</v>
       </c>
       <c r="G38">
-        <v>-2.567534470196574</v>
+        <v>-1.489117639687907</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.029519336739452</v>
       </c>
       <c r="E39">
-        <v>-21.351557770017</v>
+        <v>-18.6270466680422</v>
       </c>
       <c r="F39">
-        <v>-0.996530274652327</v>
+        <v>0.3974397638394587</v>
       </c>
       <c r="G39">
-        <v>-3.755560152964972</v>
+        <v>-1.146317270187454</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.187255067034628</v>
       </c>
       <c r="E40">
-        <v>-21.12284719025961</v>
+        <v>-17.09149094525527</v>
       </c>
       <c r="F40">
-        <v>-0.9386605278927536</v>
+        <v>0.5942449481313707</v>
       </c>
       <c r="G40">
-        <v>-3.218410897036065</v>
+        <v>-1.582706762083103</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.378618114921712</v>
       </c>
       <c r="E41">
-        <v>-19.6178269677064</v>
+        <v>-16.83338604071409</v>
       </c>
       <c r="F41">
-        <v>-1.067831998848294</v>
+        <v>0.4928130163933769</v>
       </c>
       <c r="G41">
-        <v>-3.608969196486044</v>
+        <v>-1.147128353844575</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.591342195460538</v>
       </c>
       <c r="E42">
-        <v>-20.71754423809911</v>
+        <v>-15.80680815401927</v>
       </c>
       <c r="F42">
-        <v>-1.264716706410875</v>
+        <v>0.05149365561271792</v>
       </c>
       <c r="G42">
-        <v>-3.095894227718716</v>
+        <v>-0.8748061883296665</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.814770467777993</v>
       </c>
       <c r="E43">
-        <v>-20.43556974706349</v>
+        <v>-14.9422092541048</v>
       </c>
       <c r="F43">
-        <v>-1.642097700839052</v>
+        <v>0.3201887049565851</v>
       </c>
       <c r="G43">
-        <v>-2.660143671112146</v>
+        <v>-0.5332605155885974</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.039586265021533</v>
       </c>
       <c r="E44">
-        <v>-17.92282367510939</v>
+        <v>-14.21129996384479</v>
       </c>
       <c r="F44">
-        <v>-1.249435812931433</v>
+        <v>0.4436311869543647</v>
       </c>
       <c r="G44">
-        <v>-2.48887921872903</v>
+        <v>-0.5053857221479341</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.253255459450473</v>
       </c>
       <c r="E45">
-        <v>-17.32873769851712</v>
+        <v>-13.59430896572172</v>
       </c>
       <c r="F45">
-        <v>-1.079064660830256</v>
+        <v>0.406936996112555</v>
       </c>
       <c r="G45">
-        <v>-2.43900253963437</v>
+        <v>-0.4146105634611181</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.448683035825564</v>
       </c>
       <c r="E46">
-        <v>-17.28365673977076</v>
+        <v>-12.64842848584358</v>
       </c>
       <c r="F46">
-        <v>-1.116494441925751</v>
+        <v>-0.02226583466735566</v>
       </c>
       <c r="G46">
-        <v>-2.065513412984874</v>
+        <v>-0.00715855012423822</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.618364417709207</v>
       </c>
       <c r="E47">
-        <v>-17.12454427703726</v>
+        <v>-12.04194354741832</v>
       </c>
       <c r="F47">
-        <v>-1.274194886233707</v>
+        <v>0.03345844051896708</v>
       </c>
       <c r="G47">
-        <v>-2.449976998097054</v>
+        <v>0.1086476433850072</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.754556474038122</v>
       </c>
       <c r="E48">
-        <v>-15.87852106840474</v>
+        <v>-10.79436707220117</v>
       </c>
       <c r="F48">
-        <v>-0.9876302952766491</v>
+        <v>-0.2461379238457417</v>
       </c>
       <c r="G48">
-        <v>-2.399358756801598</v>
+        <v>0.4209347146499975</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.853870582245782</v>
       </c>
       <c r="E49">
-        <v>-15.78034375191844</v>
+        <v>-10.8861954681287</v>
       </c>
       <c r="F49">
-        <v>-1.262687206274017</v>
+        <v>-0.08592752630730327</v>
       </c>
       <c r="G49">
-        <v>-3.376237845075279</v>
+        <v>0.4368087805108029</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.912344482317327</v>
       </c>
       <c r="E50">
-        <v>-14.46873012575882</v>
+        <v>-9.830060231585815</v>
       </c>
       <c r="F50">
-        <v>-1.279062373092557</v>
+        <v>-0.1221213832378221</v>
       </c>
       <c r="G50">
-        <v>-3.152852163721877</v>
+        <v>-0.1070277774074321</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.927452259621543</v>
       </c>
       <c r="E51">
-        <v>-13.76957449524059</v>
+        <v>-9.202463547336789</v>
       </c>
       <c r="F51">
-        <v>-1.234363668037496</v>
+        <v>-0.06619332967041065</v>
       </c>
       <c r="G51">
-        <v>-1.905935186355385</v>
+        <v>0.1586004650270701</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.89997448611915</v>
       </c>
       <c r="E52">
-        <v>-13.05038489571242</v>
+        <v>-8.135921877524273</v>
       </c>
       <c r="F52">
-        <v>-1.351573513696612</v>
+        <v>-0.1973694497407264</v>
       </c>
       <c r="G52">
-        <v>-1.548273777929143</v>
+        <v>-0.2100420229529336</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.829715204304815</v>
       </c>
       <c r="E53">
-        <v>-12.06560029563439</v>
+        <v>-7.483649538407451</v>
       </c>
       <c r="F53">
-        <v>-1.097080823473742</v>
+        <v>0.05521799545570449</v>
       </c>
       <c r="G53">
-        <v>-2.854211161169763</v>
+        <v>0.2317204843529528</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.717941187397518</v>
       </c>
       <c r="E54">
-        <v>-12.86791909252136</v>
+        <v>-6.728295545454027</v>
       </c>
       <c r="F54">
-        <v>-1.520365797528053</v>
+        <v>-0.1271967903147746</v>
       </c>
       <c r="G54">
-        <v>-3.487074909730079</v>
+        <v>0.3106505111002565</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.568996176186465</v>
       </c>
       <c r="E55">
-        <v>-11.63821650421248</v>
+        <v>-5.829597236261806</v>
       </c>
       <c r="F55">
-        <v>-1.538101143621991</v>
+        <v>-0.1947667193611303</v>
       </c>
       <c r="G55">
-        <v>-2.825819922624973</v>
+        <v>-0.1677166982333515</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.385586852144709</v>
       </c>
       <c r="E56">
-        <v>-11.00260442096988</v>
+        <v>-5.066567479865382</v>
       </c>
       <c r="F56">
-        <v>-1.138429610751882</v>
+        <v>-0.2748797876206761</v>
       </c>
       <c r="G56">
-        <v>-3.84841433425045</v>
+        <v>-1.07669980804212</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.172286034283463</v>
       </c>
       <c r="E57">
-        <v>-11.58694964997165</v>
+        <v>-4.905190780128041</v>
       </c>
       <c r="F57">
-        <v>-1.374153980729524</v>
+        <v>-0.326000825149642</v>
       </c>
       <c r="G57">
-        <v>-3.934786467370035</v>
+        <v>-1.089319607637822</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.935548549477093</v>
       </c>
       <c r="E58">
-        <v>-10.10554541936843</v>
+        <v>-4.093221805130723</v>
       </c>
       <c r="F58">
-        <v>-1.469031041209165</v>
+        <v>-0.2269893829626283</v>
       </c>
       <c r="G58">
-        <v>-3.674246533429393</v>
+        <v>-0.7888544944935687</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.680275371225657</v>
       </c>
       <c r="E59">
-        <v>-8.99180799344798</v>
+        <v>-3.347848568890205</v>
       </c>
       <c r="F59">
-        <v>-1.293104028937412</v>
+        <v>-0.4444076617058033</v>
       </c>
       <c r="G59">
-        <v>-4.080480266007821</v>
+        <v>-1.078676203729065</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.414994360419222</v>
       </c>
       <c r="E60">
-        <v>-11.17500342644189</v>
+        <v>-3.632318249104042</v>
       </c>
       <c r="F60">
-        <v>-1.220367572399795</v>
+        <v>-0.5305968048648835</v>
       </c>
       <c r="G60">
-        <v>-3.301045424241813</v>
+        <v>-0.8748889519681483</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.148265292780053</v>
       </c>
       <c r="E61">
-        <v>-8.384820394407859</v>
+        <v>-2.63438748898174</v>
       </c>
       <c r="F61">
-        <v>-1.676053309047206</v>
+        <v>-0.5787696828072859</v>
       </c>
       <c r="G61">
-        <v>-4.446593497195821</v>
+        <v>-1.973311409170632</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.8861005614717046</v>
       </c>
       <c r="E62">
-        <v>-7.687707105667084</v>
+        <v>-2.660702451440313</v>
       </c>
       <c r="F62">
-        <v>-1.498012303163508</v>
+        <v>-0.4310982826450236</v>
       </c>
       <c r="G62">
-        <v>-4.225737072634423</v>
+        <v>-1.943413872405474</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.6382618179911135</v>
       </c>
       <c r="E63">
-        <v>-9.198546417320154</v>
+        <v>-1.665805768903151</v>
       </c>
       <c r="F63">
-        <v>-1.472729701662665</v>
+        <v>-0.5378234820869063</v>
       </c>
       <c r="G63">
-        <v>-3.420099262925083</v>
+        <v>-2.515515868138006</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4109226729310141</v>
       </c>
       <c r="E64">
-        <v>-7.944145531773442</v>
+        <v>-1.399196390175566</v>
       </c>
       <c r="F64">
-        <v>-2.030684021124897</v>
+        <v>-0.4635222395254019</v>
       </c>
       <c r="G64">
-        <v>-4.624783610847093</v>
+        <v>-2.519803024611362</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.2083410910921236</v>
       </c>
       <c r="E65">
-        <v>-7.626699503835749</v>
+        <v>-1.84940369059613</v>
       </c>
       <c r="F65">
-        <v>-1.872041723079958</v>
+        <v>-0.7467087482138437</v>
       </c>
       <c r="G65">
-        <v>-5.507401535981105</v>
+        <v>-2.764243775594529</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.03647710834298498</v>
       </c>
       <c r="E66">
-        <v>-6.79720080595474</v>
+        <v>-1.327601216114298</v>
       </c>
       <c r="F66">
-        <v>-1.494736938452839</v>
+        <v>-0.6174395299047725</v>
       </c>
       <c r="G66">
-        <v>-4.054108460241987</v>
+        <v>-3.383762715086042</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1032813066618126</v>
       </c>
       <c r="E67">
-        <v>-8.236481171338601</v>
+        <v>-1.034323653955542</v>
       </c>
       <c r="F67">
-        <v>-1.898001100748889</v>
+        <v>-0.9643896194237062</v>
       </c>
       <c r="G67">
-        <v>-6.069277256542829</v>
+        <v>-3.419791382189931</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.2089910725296595</v>
       </c>
       <c r="E68">
-        <v>-8.492887898126904</v>
+        <v>-0.8968618254527085</v>
       </c>
       <c r="F68">
-        <v>-2.129076672862019</v>
+        <v>-0.6447806244015729</v>
       </c>
       <c r="G68">
-        <v>-5.692401441806658</v>
+        <v>-3.096887391380498</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.2796949088471716</v>
       </c>
       <c r="E69">
-        <v>-7.270815788520951</v>
+        <v>-0.5976519623439051</v>
       </c>
       <c r="F69">
-        <v>-1.477719786897129</v>
+        <v>-1.050215109292957</v>
       </c>
       <c r="G69">
-        <v>-4.653939585411455</v>
+        <v>-3.586884547193566</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.3168511919857552</v>
       </c>
       <c r="E70">
-        <v>-6.582433397666965</v>
+        <v>-0.7401222830992221</v>
       </c>
       <c r="F70">
-        <v>-1.460899786783285</v>
+        <v>-1.221794021067416</v>
       </c>
       <c r="G70">
-        <v>-5.578094925426702</v>
+        <v>-3.172771716231672</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.319358504003707</v>
       </c>
       <c r="E71">
-        <v>-7.307125093114452</v>
+        <v>-0.2038875619549445</v>
       </c>
       <c r="F71">
-        <v>-2.252877009577809</v>
+        <v>-1.239314820004028</v>
       </c>
       <c r="G71">
-        <v>-4.892517360244572</v>
+        <v>-3.597547814375558</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.2884733176371234</v>
       </c>
       <c r="E72">
-        <v>-7.533200100999379</v>
+        <v>-1.101231857418872</v>
       </c>
       <c r="F72">
-        <v>-1.748740891908057</v>
+        <v>-1.135158387878227</v>
       </c>
       <c r="G72">
-        <v>-5.434288137746302</v>
+        <v>-3.182282913565998</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.224996676152617</v>
       </c>
       <c r="E73">
-        <v>-7.985060294432743</v>
+        <v>-0.8399887203903765</v>
       </c>
       <c r="F73">
-        <v>-2.53869689823975</v>
+        <v>-1.49784414458074</v>
       </c>
       <c r="G73">
-        <v>-4.094391178363838</v>
+        <v>-2.68515484266134</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1285264081168221</v>
       </c>
       <c r="E74">
-        <v>-7.105897822109612</v>
+        <v>-1.881533213680551</v>
       </c>
       <c r="F74">
-        <v>-2.65919536248798</v>
+        <v>-1.526509798554617</v>
       </c>
       <c r="G74">
-        <v>-4.62057259692114</v>
+        <v>-3.167398700821435</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.00193075639064333</v>
       </c>
       <c r="E75">
-        <v>-7.587578016883485</v>
+        <v>-1.497319364973767</v>
       </c>
       <c r="F75">
-        <v>-2.332533647398412</v>
+        <v>-1.485132018417379</v>
       </c>
       <c r="G75">
-        <v>-4.384679674520371</v>
+        <v>-2.534975254817842</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.1550643540561778</v>
       </c>
       <c r="E76">
-        <v>-9.302742075762641</v>
+        <v>-2.618207251352334</v>
       </c>
       <c r="F76">
-        <v>-2.384474768656149</v>
+        <v>-1.732201708343762</v>
       </c>
       <c r="G76">
-        <v>-4.208687763107176</v>
+        <v>-2.756046864839294</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3408799414024298</v>
       </c>
       <c r="E77">
-        <v>-9.090392872594963</v>
+        <v>-2.449209129860084</v>
       </c>
       <c r="F77">
-        <v>-2.45673325720235</v>
+        <v>-1.342461472265817</v>
       </c>
       <c r="G77">
-        <v>-3.503150918868779</v>
+        <v>-2.515734364143598</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5523600866469086</v>
       </c>
       <c r="E78">
-        <v>-8.556644283680896</v>
+        <v>-3.197285865083181</v>
       </c>
       <c r="F78">
-        <v>-2.869941141801605</v>
+        <v>-1.73981440477549</v>
       </c>
       <c r="G78">
-        <v>-3.919134208060361</v>
+        <v>-2.011184050139894</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7890211351030834</v>
       </c>
       <c r="E79">
-        <v>-11.81384884012597</v>
+        <v>-4.564083475500271</v>
       </c>
       <c r="F79">
-        <v>-2.781199798674499</v>
+        <v>-1.675605990649695</v>
       </c>
       <c r="G79">
-        <v>-3.246583639575262</v>
+        <v>-1.365336341974557</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.046483659431884</v>
       </c>
       <c r="E80">
-        <v>-10.54434549376368</v>
+        <v>-5.40478108960225</v>
       </c>
       <c r="F80">
-        <v>-2.789104908799415</v>
+        <v>-1.759856754086224</v>
       </c>
       <c r="G80">
-        <v>-3.162350118874046</v>
+        <v>-1.343589368327085</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.320895363180627</v>
       </c>
       <c r="E81">
-        <v>-10.23997317028613</v>
+        <v>-5.613548269829861</v>
       </c>
       <c r="F81">
-        <v>-2.724106232171349</v>
+        <v>-1.853000041591806</v>
       </c>
       <c r="G81">
-        <v>-3.363161190195158</v>
+        <v>-0.9856465635300051</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.608327119278659</v>
       </c>
       <c r="E82">
-        <v>-13.5551512509774</v>
+        <v>-6.471635224121295</v>
       </c>
       <c r="F82">
-        <v>-2.927194583213495</v>
+        <v>-2.058011861743253</v>
       </c>
       <c r="G82">
-        <v>-2.664980378145022</v>
+        <v>-0.5316449693654332</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.899645488560697</v>
       </c>
       <c r="E83">
-        <v>-13.22345864381158</v>
+        <v>-8.22050471503954</v>
       </c>
       <c r="F83">
-        <v>-2.995718791507876</v>
+        <v>-2.157491331512848</v>
       </c>
       <c r="G83">
-        <v>-2.504802942772924</v>
+        <v>0.1897460774605334</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.18791855945164</v>
       </c>
       <c r="E84">
-        <v>-13.67253835420423</v>
+        <v>-9.538159325525392</v>
       </c>
       <c r="F84">
-        <v>-3.265518054599675</v>
+        <v>-2.00142359935581</v>
       </c>
       <c r="G84">
-        <v>-1.675620533188288</v>
+        <v>0.1456727846962161</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.462932928480381</v>
       </c>
       <c r="E85">
-        <v>-15.50951383541571</v>
+        <v>-9.871844461254589</v>
       </c>
       <c r="F85">
-        <v>-3.336528193469857</v>
+        <v>-2.429383879031521</v>
       </c>
       <c r="G85">
-        <v>-1.886028876027747</v>
+        <v>0.6544539758991085</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.711220082361286</v>
       </c>
       <c r="E86">
-        <v>-15.820819252599</v>
+        <v>-11.85921509273481</v>
       </c>
       <c r="F86">
-        <v>-3.608169745665482</v>
+        <v>-2.341888400478227</v>
       </c>
       <c r="G86">
-        <v>-2.145085685566796</v>
+        <v>1.332390801976602</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.921420910849024</v>
       </c>
       <c r="E87">
-        <v>-18.44994710655023</v>
+        <v>-13.06105398047449</v>
       </c>
       <c r="F87">
-        <v>-3.743366761108987</v>
+        <v>-2.357475789896705</v>
       </c>
       <c r="G87">
-        <v>-1.730433235682001</v>
+        <v>0.8596051724222047</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.080807732793307</v>
       </c>
       <c r="E88">
-        <v>-17.94520339365529</v>
+        <v>-16.02004493809245</v>
       </c>
       <c r="F88">
-        <v>-3.520487884446557</v>
+        <v>-2.420156694531738</v>
       </c>
       <c r="G88">
-        <v>-1.317032172011051</v>
+        <v>1.82897263286728</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.178015003551583</v>
       </c>
       <c r="E89">
-        <v>-20.44866609389368</v>
+        <v>-16.57281764631274</v>
       </c>
       <c r="F89">
-        <v>-3.416898055624271</v>
+        <v>-2.535600460888085</v>
       </c>
       <c r="G89">
-        <v>-1.560065941140027</v>
+        <v>1.805322095534726</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.205850445572298</v>
       </c>
       <c r="E90">
-        <v>-21.82964688490279</v>
+        <v>-19.22237344651257</v>
       </c>
       <c r="F90">
-        <v>-3.567746244776269</v>
+        <v>-2.959061877199193</v>
       </c>
       <c r="G90">
-        <v>-1.769404977770302</v>
+        <v>1.875204401323202</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.159692148998181</v>
       </c>
       <c r="E91">
-        <v>-24.08401634387526</v>
+        <v>-21.13498802907417</v>
       </c>
       <c r="F91">
-        <v>-3.819243558470616</v>
+        <v>-2.997703559804984</v>
       </c>
       <c r="G91">
-        <v>-1.140533747130347</v>
+        <v>1.224963599227251</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.038328565022765</v>
       </c>
       <c r="E92">
-        <v>-25.21962177077875</v>
+        <v>-22.74540848415591</v>
       </c>
       <c r="F92">
-        <v>-3.94884495210821</v>
+        <v>-3.181828924262244</v>
       </c>
       <c r="G92">
-        <v>-0.7734736999181148</v>
+        <v>1.536820299572137</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.846509578164362</v>
       </c>
       <c r="E93">
-        <v>-28.21502618789238</v>
+        <v>-25.40203776075573</v>
       </c>
       <c r="F93">
-        <v>-4.216420048723492</v>
+        <v>-2.758152960793812</v>
       </c>
       <c r="G93">
-        <v>-1.062030780757609</v>
+        <v>1.593182337378229</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.591693025836368</v>
       </c>
       <c r="E94">
-        <v>-30.46561663530545</v>
+        <v>-27.00262689876682</v>
       </c>
       <c r="F94">
-        <v>-4.387932691105727</v>
+        <v>-3.210146663926945</v>
       </c>
       <c r="G94">
-        <v>-2.20716172497367</v>
+        <v>0.7998134094374278</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.284992177479059</v>
       </c>
       <c r="E95">
-        <v>-31.69037639423496</v>
+        <v>-29.60923917995191</v>
       </c>
       <c r="F95">
-        <v>-4.341218568159654</v>
+        <v>-3.319540863140648</v>
       </c>
       <c r="G95">
-        <v>-1.853830510112795</v>
+        <v>0.9015564054958491</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.941147645386097</v>
       </c>
       <c r="E96">
-        <v>-32.69139330939348</v>
+        <v>-31.90641177524488</v>
       </c>
       <c r="F96">
-        <v>-4.612629834217302</v>
+        <v>-3.480249109488168</v>
       </c>
       <c r="G96">
-        <v>-2.118627805616941</v>
+        <v>0.6925285601462664</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.577353630620225</v>
       </c>
       <c r="E97">
-        <v>-37.03523916753412</v>
+        <v>-35.35805542015729</v>
       </c>
       <c r="F97">
-        <v>-4.608438295159136</v>
+        <v>-3.554329177953126</v>
       </c>
       <c r="G97">
-        <v>-2.940871311751264</v>
+        <v>0.2441085457609056</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.207021613603768</v>
       </c>
       <c r="E98">
-        <v>-39.11547068701562</v>
+        <v>-37.32836276157661</v>
       </c>
       <c r="F98">
-        <v>-4.408668383932604</v>
+        <v>-3.668948718743688</v>
       </c>
       <c r="G98">
-        <v>-3.907136791026042</v>
+        <v>-0.05387034768335467</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.8546679608782008</v>
       </c>
       <c r="E99">
-        <v>-41.09017064822238</v>
+        <v>-39.675375741798</v>
       </c>
       <c r="F99">
-        <v>-4.758135053621243</v>
+        <v>-3.966982884759908</v>
       </c>
       <c r="G99">
-        <v>-3.735786264458905</v>
+        <v>-0.6739918064630156</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.5244871484497899</v>
       </c>
       <c r="E100">
-        <v>-44.30385883369075</v>
+        <v>-42.88165760802681</v>
       </c>
       <c r="F100">
-        <v>-5.131674080035235</v>
+        <v>-4.064314397854044</v>
       </c>
       <c r="G100">
-        <v>-4.003619330222562</v>
+        <v>-1.664579863814819</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.247296422533415</v>
       </c>
       <c r="E101">
-        <v>-44.6030958676436</v>
+        <v>-44.50329509322555</v>
       </c>
       <c r="F101">
-        <v>-4.704760028389259</v>
+        <v>-4.067400066429472</v>
       </c>
       <c r="G101">
-        <v>-4.960833777992972</v>
+        <v>-2.034129441272583</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.007455276963394861</v>
       </c>
       <c r="E102">
-        <v>-48.03858418153365</v>
+        <v>-47.93994722493558</v>
       </c>
       <c r="F102">
-        <v>-5.473900818623406</v>
+        <v>-3.966112270619565</v>
       </c>
       <c r="G102">
-        <v>-5.076378438404615</v>
+        <v>-2.605767960629617</v>
       </c>
     </row>
   </sheetData>
